--- a/docs/02_機能毎のテスト/試験項目表_JMSS.xlsx
+++ b/docs/02_機能毎のテスト/試験項目表_JMSS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Git\home\issues\TSF4J5-4861_spring-func\docs\02_機能毎のテスト\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\terasolunaorg\spring-functionaltest\docs\02_機能毎のテスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{562C8CCD-5DE4-4FFB-A132-3358D525F4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6445F4D-9FA9-4FD8-8AA0-6C6EA382BAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3135" yWindow="2490" windowWidth="22890" windowHeight="12165" tabRatio="707" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22450" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="707" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="大中項目" sheetId="1" r:id="rId1"/>
@@ -2936,31 +2936,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>&lt;jms:annotation-driven&gt;を定義する。
-非同期受信用のメソッドに@Header("jms_priority")を指定した引数を定義する。
-非同期受信用のメソッドに@Headersを指定した引数を定義する。
-※キュー「jms/queue/TestQueue0303001」（JNDI名)</t>
-    <rPh sb="24" eb="26">
-      <t>テイギ</t>
-    </rPh>
-    <rPh sb="31" eb="34">
-      <t>ヒドウキ</t>
-    </rPh>
-    <rPh sb="34" eb="37">
-      <t>ジュシンヨウ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="71" eb="73">
-      <t>ヒキスウ</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t>テイギ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>JMSPriorityに2を設定したメッセージを送信する。</t>
     <rPh sb="14" eb="16">
       <t>セッテイ</t>
@@ -3501,6 +3476,31 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>&lt;jms:annotation-driven&gt;を定義する。
+非同期受信用のメソッドに@Header("JmsHeaders.PRIORITY")を指定した引数を定義する。
+非同期受信用のメソッドに@Headersを指定した引数を定義する。
+※キュー「jms/queue/TestQueue0303001」（JNDI名)</t>
+    <rPh sb="24" eb="26">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>ヒドウキ</t>
+    </rPh>
+    <rPh sb="34" eb="37">
+      <t>ジュシンヨウ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -3508,7 +3508,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="[&lt;=999]000;[&lt;=9999]000\-00;000\-0000"/>
-    <numFmt numFmtId="180" formatCode="00"/>
+    <numFmt numFmtId="177" formatCode="00"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -3768,7 +3768,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3859,6 +3859,12 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3901,109 +3907,13 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <border>
         <left style="thin">
@@ -4478,15 +4388,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.25" customWidth="1"/>
-    <col min="3" max="3" width="13.625" customWidth="1"/>
+    <col min="1" max="1" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.265625" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" customWidth="1"/>
     <col min="4" max="4" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4497,7 +4407,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -4509,7 +4419,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -4523,7 +4433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="str">
         <f>IF(B5="","",($B$1&amp;TEXT(IF(B5="","",COUNTA($B$5:B5)),"00")))</f>
         <v>JMSS01</v>
@@ -4539,7 +4449,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="str">
         <f>IF(B6="","",($B$1&amp;TEXT(IF(B6="","",COUNTA($B$5:B6)),"00")))</f>
         <v/>
@@ -4553,7 +4463,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="str">
         <f>IF(B7="","",($B$1&amp;TEXT(IF(B7="","",COUNTA($B$5:B7)),"00")))</f>
         <v/>
@@ -4567,7 +4477,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="str">
         <f>IF(B8="","",($B$1&amp;TEXT(IF(B8="","",COUNTA($B$5:B8)),"00")))</f>
         <v>JMSS02</v>
@@ -4583,7 +4493,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="15"/>
       <c r="B9" s="20"/>
       <c r="C9" s="16" t="str">
@@ -4594,7 +4504,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="str">
         <f>IF(B10="","",($B$1&amp;TEXT(IF(B10="","",COUNTA($B$5:B10)),"00")))</f>
         <v>JMSS03</v>
@@ -4610,7 +4520,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="15"/>
       <c r="B11" s="20"/>
       <c r="C11" s="16" t="str">
@@ -4621,7 +4531,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="str">
         <f>IF(B12="","",($B$1&amp;TEXT(IF(B12="","",COUNTA($B$5:B12)),"00")))</f>
         <v/>
@@ -4635,7 +4545,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="str">
         <f>IF(B13="","",($B$1&amp;TEXT(IF(B13="","",COUNTA($B$5:B13)),"00")))</f>
         <v>JMSS04</v>
@@ -4651,7 +4561,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="15"/>
       <c r="B14" s="20"/>
       <c r="C14" s="16" t="str">
@@ -4662,7 +4572,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="str">
         <f>IF(B15="","",($B$1&amp;TEXT(IF(B15="","",COUNTA($B$5:B15)),"00")))</f>
         <v/>
@@ -4676,7 +4586,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="str">
         <f>IF(B16="","",($B$1&amp;TEXT(IF(B16="","",COUNTA($B$5:B16)),"00")))</f>
         <v/>
@@ -4690,7 +4600,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="str">
         <f>IF(B17="","",($B$1&amp;TEXT(IF(B17="","",COUNTA($B$5:B17)),"00")))</f>
         <v>JMSS05</v>
@@ -4706,7 +4616,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="str">
         <f>IF(B18="","",($B$1&amp;TEXT(IF(B18="","",COUNTA($B$5:B18)),"00")))</f>
         <v>JMSS06</v>
@@ -4722,7 +4632,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="15"/>
       <c r="B19" s="20"/>
       <c r="C19" s="16" t="str">
@@ -4733,7 +4643,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="15"/>
       <c r="B20" s="20"/>
       <c r="C20" s="16" t="str">
@@ -4744,7 +4654,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="str">
         <f>IF(B21="","",($B$1&amp;TEXT(IF(B21="","",COUNTA($B$5:B21)),"00")))</f>
         <v/>
@@ -4758,7 +4668,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="str">
         <f>IF(B22="","",($B$1&amp;TEXT(IF(B22="","",COUNTA($B$5:B22)),"00")))</f>
         <v>JMSS07</v>
@@ -4774,7 +4684,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="str">
         <f>IF(B23="","",($B$1&amp;TEXT(IF(B23="","",COUNTA($B$5:B23)),"00")))</f>
         <v>JMSS08</v>
@@ -4790,7 +4700,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="25"/>
       <c r="B24" s="26"/>
       <c r="C24" s="16" t="str">
@@ -4801,7 +4711,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="str">
         <f>IF(B25="","",($B$1&amp;TEXT(IF(B25="","",COUNTA($B$5:B25)),"00")))</f>
         <v>JMSS09</v>
@@ -4820,12 +4730,12 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A5:A25">
-    <cfRule type="expression" dxfId="15" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>$A5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4843,25 +4753,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="25.125" customWidth="1"/>
-    <col min="5" max="5" width="42.75" customWidth="1"/>
-    <col min="6" max="6" width="41.75" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" customWidth="1"/>
+    <col min="2" max="2" width="8.59765625" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" customWidth="1"/>
+    <col min="4" max="4" width="25.1328125" customWidth="1"/>
+    <col min="5" max="5" width="42.73046875" customWidth="1"/>
+    <col min="6" max="6" width="41.73046875" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="43.5" customWidth="1"/>
-    <col min="9" max="9" width="19.25" customWidth="1"/>
+    <col min="8" max="8" width="43.46484375" customWidth="1"/>
+    <col min="9" max="9" width="19.265625" customWidth="1"/>
     <col min="10" max="10" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -4881,12 +4791,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="36">
+      <c r="B2" s="35"/>
+      <c r="C2" s="38">
         <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
         <v>1</v>
       </c>
@@ -4902,10 +4812,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="37"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="39"/>
       <c r="D3" s="17" t="str">
         <f>大中項目!B2</f>
         <v>JMS</v>
@@ -4918,7 +4828,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -4928,31 +4838,31 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A5" s="38" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="40"/>
-    </row>
-    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+    </row>
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="43"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="45"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -4962,7 +4872,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -4991,7 +4901,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="str">
         <f>大中項目!C25</f>
         <v>JMSS0901</v>
@@ -5059,25 +4969,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="25.125" customWidth="1"/>
-    <col min="5" max="5" width="42.75" customWidth="1"/>
-    <col min="6" max="6" width="41.75" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" customWidth="1"/>
+    <col min="2" max="2" width="8.59765625" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" customWidth="1"/>
+    <col min="4" max="4" width="25.1328125" customWidth="1"/>
+    <col min="5" max="5" width="42.73046875" customWidth="1"/>
+    <col min="6" max="6" width="41.73046875" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="45.5" customWidth="1"/>
-    <col min="9" max="9" width="21.625" customWidth="1"/>
-    <col min="10" max="10" width="40.375" customWidth="1"/>
+    <col min="8" max="8" width="45.46484375" customWidth="1"/>
+    <col min="9" max="9" width="21.59765625" customWidth="1"/>
+    <col min="10" max="10" width="40.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -5097,12 +5007,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="36">
+      <c r="B2" s="35"/>
+      <c r="C2" s="38">
         <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
         <v>3</v>
       </c>
@@ -5118,10 +5028,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="37"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="39"/>
       <c r="D3" s="17" t="str">
         <f>大中項目!B2</f>
         <v>JMS</v>
@@ -5134,7 +5044,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -5144,31 +5054,31 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A5" s="38" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="40"/>
-    </row>
-    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+    </row>
+    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="43"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="45"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -5178,7 +5088,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -5207,9 +5117,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="150" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="47" t="s">
-        <v>241</v>
+    <row r="9" spans="1:10" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
+        <v>240</v>
       </c>
       <c r="B9" s="18">
         <f ca="1">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
@@ -5234,12 +5144,12 @@
         <v>106</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="47" t="s">
-        <v>242</v>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="30" t="s">
+        <v>241</v>
       </c>
       <c r="B10" s="18">
         <f t="shared" ref="B10" ca="1" si="0">IF(A10&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B10)-1,COLUMN(B10),4))+1)</f>
@@ -5264,12 +5174,12 @@
         <v>106</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="103.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="48" t="s">
-        <v>243</v>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="31" t="s">
+        <v>242</v>
       </c>
       <c r="B11" s="18">
         <f t="shared" ref="B11" ca="1" si="1">IF(A11&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B11)-1,COLUMN(B11),4))+1)</f>
@@ -5294,7 +5204,7 @@
         <v>106</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J11" s="21"/>
     </row>
@@ -5308,18 +5218,8 @@
     <mergeCell ref="A6:H6"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="B10:B11">
-    <cfRule type="expression" dxfId="13" priority="25">
-      <formula>B10&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9:B11">
-    <cfRule type="expression" dxfId="12" priority="22">
-      <formula>B9&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:A11">
-    <cfRule type="expression" dxfId="11" priority="1">
+  <conditionalFormatting sqref="A9:B11">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>A9&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5348,25 +5248,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="25.125" customWidth="1"/>
-    <col min="5" max="5" width="42.75" customWidth="1"/>
-    <col min="6" max="6" width="41.75" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" customWidth="1"/>
+    <col min="2" max="2" width="8.59765625" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" customWidth="1"/>
+    <col min="4" max="4" width="25.1328125" customWidth="1"/>
+    <col min="5" max="5" width="42.73046875" customWidth="1"/>
+    <col min="6" max="6" width="41.73046875" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="44.5" customWidth="1"/>
-    <col min="9" max="9" width="22.75" customWidth="1"/>
-    <col min="10" max="10" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.46484375" customWidth="1"/>
+    <col min="9" max="9" width="22.73046875" customWidth="1"/>
+    <col min="10" max="10" width="18.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -5386,12 +5286,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="36">
+      <c r="B2" s="35"/>
+      <c r="C2" s="38">
         <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
         <v>2</v>
       </c>
@@ -5407,10 +5307,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="37"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="39"/>
       <c r="D3" s="17" t="str">
         <f>大中項目!B2</f>
         <v>JMS</v>
@@ -5423,7 +5323,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -5433,31 +5333,31 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A5" s="38" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="40"/>
-    </row>
-    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+    </row>
+    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="43"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="45"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -5467,7 +5367,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -5496,65 +5396,65 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="120.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="47" t="s">
-        <v>244</v>
+    <row r="9" spans="1:10" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
+        <v>243</v>
       </c>
       <c r="B9" s="18">
         <f ca="1">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
         <v>1</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D9" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="E9" s="45" t="s">
+      <c r="E9" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="F9" s="45" t="s">
+      <c r="F9" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="H9" s="45" t="s">
-        <v>238</v>
+      <c r="H9" s="13" t="s">
+        <v>237</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J9" s="29"/>
     </row>
-    <row r="10" spans="1:10" ht="120.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="48" t="s">
-        <v>245</v>
+    <row r="10" spans="1:10" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="31" t="s">
+        <v>244</v>
       </c>
       <c r="B10" s="18">
         <f ca="1">IF(A10&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B10)-1,COLUMN(B10),4))+1)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="45" t="s">
+      <c r="E10" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="G10" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="H10" s="45" t="s">
-        <v>239</v>
+      <c r="H10" s="13" t="s">
+        <v>238</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J10" s="29"/>
     </row>
@@ -5567,13 +5467,8 @@
     <mergeCell ref="A6:H6"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="B9:B10">
-    <cfRule type="expression" dxfId="10" priority="34">
-      <formula>B9&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:A10">
-    <cfRule type="expression" dxfId="9" priority="1">
+  <conditionalFormatting sqref="A9:B10">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>A9&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5602,25 +5497,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="25.125" customWidth="1"/>
-    <col min="5" max="5" width="42.75" customWidth="1"/>
-    <col min="6" max="6" width="41.75" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" customWidth="1"/>
+    <col min="2" max="2" width="8.59765625" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" customWidth="1"/>
+    <col min="4" max="4" width="25.1328125" customWidth="1"/>
+    <col min="5" max="5" width="42.73046875" customWidth="1"/>
+    <col min="6" max="6" width="41.73046875" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="43.5" customWidth="1"/>
-    <col min="9" max="9" width="19.25" customWidth="1"/>
+    <col min="8" max="8" width="43.46484375" customWidth="1"/>
+    <col min="9" max="9" width="19.265625" customWidth="1"/>
     <col min="10" max="10" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -5640,12 +5535,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="36">
+      <c r="B2" s="35"/>
+      <c r="C2" s="38">
         <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
         <v>7</v>
       </c>
@@ -5661,10 +5556,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="37"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="39"/>
       <c r="D3" s="17" t="str">
         <f>大中項目!B2</f>
         <v>JMS</v>
@@ -5677,7 +5572,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -5687,31 +5582,31 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A5" s="38" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="40"/>
-    </row>
-    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+    </row>
+    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="43"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="45"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -5721,7 +5616,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -5750,9 +5645,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="108.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="47" t="s">
-        <v>246</v>
+    <row r="9" spans="1:10" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
+        <v>245</v>
       </c>
       <c r="B9" s="18">
         <f ca="1">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
@@ -5777,41 +5672,41 @@
         <v>95</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J9" s="21"/>
     </row>
-    <row r="10" spans="1:10" ht="91.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="47"/>
+    <row r="10" spans="1:10" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="30"/>
       <c r="B10" s="18">
         <f ca="1">IF(A10&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B10)-1,COLUMN(B10),4))+1)</f>
         <v>2</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="45" t="s">
+      <c r="E10" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="G10" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="H10" s="45" t="s">
-        <v>240</v>
+      <c r="H10" s="13" t="s">
+        <v>239</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10" ht="99.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="47"/>
+    <row r="11" spans="1:10" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="30"/>
       <c r="B11" s="18">
         <f ca="1">IF(A11&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B11)-1,COLUMN(B11),4))+1)</f>
         <v>3</v>
@@ -5835,12 +5730,12 @@
         <v>95</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J11" s="21"/>
     </row>
-    <row r="12" spans="1:10" ht="102" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="47"/>
+    <row r="12" spans="1:10" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="30"/>
       <c r="B12" s="18">
         <f ca="1">IF(A12&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B12)-1,COLUMN(B12),4))+1)</f>
         <v>4</v>
@@ -5864,13 +5759,13 @@
         <v>100</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J12" s="21"/>
     </row>
-    <row r="13" spans="1:10" ht="110.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="47" t="s">
-        <v>247</v>
+    <row r="13" spans="1:10" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="30" t="s">
+        <v>246</v>
       </c>
       <c r="B13" s="18">
         <f t="shared" ref="B13:B15" ca="1" si="0">IF(A13&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B13)-1,COLUMN(B13),4))+1)</f>
@@ -5895,13 +5790,13 @@
         <v>109</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J13" s="21"/>
     </row>
-    <row r="14" spans="1:10" ht="145.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="47" t="s">
-        <v>248</v>
+    <row r="14" spans="1:10" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="30" t="s">
+        <v>247</v>
       </c>
       <c r="B14" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -5926,12 +5821,12 @@
         <v>208</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J14" s="21"/>
     </row>
-    <row r="15" spans="1:10" ht="121.5" x14ac:dyDescent="0.15">
-      <c r="A15" s="48"/>
+    <row r="15" spans="1:10" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="31"/>
       <c r="B15" s="18">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
@@ -5955,7 +5850,7 @@
         <v>205</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -5967,13 +5862,8 @@
     <mergeCell ref="A6:H6"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="B9:B15">
-    <cfRule type="expression" dxfId="8" priority="2">
-      <formula>B9&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:A15">
-    <cfRule type="expression" dxfId="7" priority="1">
+  <conditionalFormatting sqref="A9:B15">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>A9&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6002,25 +5892,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="25.125" customWidth="1"/>
-    <col min="5" max="5" width="42.75" customWidth="1"/>
-    <col min="6" max="6" width="41.75" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" customWidth="1"/>
+    <col min="2" max="2" width="8.59765625" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" customWidth="1"/>
+    <col min="4" max="4" width="25.1328125" customWidth="1"/>
+    <col min="5" max="5" width="42.73046875" customWidth="1"/>
+    <col min="6" max="6" width="41.73046875" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="44.375" customWidth="1"/>
-    <col min="9" max="9" width="19.125" customWidth="1"/>
-    <col min="10" max="10" width="34.125" customWidth="1"/>
+    <col min="8" max="8" width="44.3984375" customWidth="1"/>
+    <col min="9" max="9" width="19.1328125" customWidth="1"/>
+    <col min="10" max="10" width="34.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -6040,12 +5930,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="36">
+      <c r="B2" s="35"/>
+      <c r="C2" s="38">
         <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
         <v>10</v>
       </c>
@@ -6061,10 +5951,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="37"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="39"/>
       <c r="D3" s="17" t="str">
         <f>大中項目!B2</f>
         <v>JMS</v>
@@ -6077,7 +5967,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -6087,31 +5977,31 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A5" s="38" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="40"/>
-    </row>
-    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+    </row>
+    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="43"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="45"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -6121,7 +6011,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -6150,37 +6040,37 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="101.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="47" t="s">
-        <v>249</v>
+    <row r="9" spans="1:10" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
+        <v>248</v>
       </c>
       <c r="B9" s="18">
         <f t="shared" ref="B9:B15" ca="1" si="0">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
         <v>1</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="49" t="s">
+      <c r="D9" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="49" t="s">
+      <c r="E9" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="F9" s="45" t="s">
+      <c r="F9" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="H9" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="I9" s="46"/>
+      <c r="H9" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="21"/>
     </row>
-    <row r="10" spans="1:10" ht="123.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="47"/>
+    <row r="10" spans="1:10" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="30"/>
       <c r="B10" s="18">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
@@ -6195,10 +6085,10 @@
         <v>74</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>110</v>
@@ -6206,8 +6096,8 @@
       <c r="I10" s="14"/>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10" ht="123.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="47"/>
+    <row r="11" spans="1:10" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="30"/>
       <c r="B11" s="18">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
@@ -6222,10 +6112,10 @@
         <v>74</v>
       </c>
       <c r="F11" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="G11" s="13" t="s">
         <v>214</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>215</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>125</v>
@@ -6233,36 +6123,36 @@
       <c r="I11" s="14"/>
       <c r="J11" s="21"/>
     </row>
-    <row r="12" spans="1:10" ht="133.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="47"/>
+    <row r="12" spans="1:10" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="30"/>
       <c r="B12" s="18">
         <f t="shared" ref="B12" ca="1" si="1">IF(A12&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B12)-1,COLUMN(B12),4))+1)</f>
         <v>4</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="49" t="s">
+      <c r="D12" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="E12" s="49" t="s">
+      <c r="E12" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="F12" s="45" t="s">
+      <c r="F12" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="G12" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="G12" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="H12" s="45" t="s">
-        <v>253</v>
-      </c>
-      <c r="I12" s="46"/>
+      <c r="H12" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="I12" s="14"/>
       <c r="J12" s="21"/>
     </row>
-    <row r="13" spans="1:10" ht="140.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="47" t="s">
-        <v>250</v>
+    <row r="13" spans="1:10" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="30" t="s">
+        <v>249</v>
       </c>
       <c r="B13" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -6289,9 +6179,9 @@
       <c r="I13" s="14"/>
       <c r="J13" s="21"/>
     </row>
-    <row r="14" spans="1:10" ht="156.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="47" t="s">
-        <v>251</v>
+    <row r="14" spans="1:10" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="30" t="s">
+        <v>250</v>
       </c>
       <c r="B14" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -6318,8 +6208,8 @@
       <c r="I14" s="14"/>
       <c r="J14" s="21"/>
     </row>
-    <row r="15" spans="1:10" ht="152.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="47"/>
+    <row r="15" spans="1:10" ht="152.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="30"/>
       <c r="B15" s="18">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
@@ -6345,8 +6235,8 @@
       <c r="I15" s="14"/>
       <c r="J15" s="21"/>
     </row>
-    <row r="16" spans="1:10" ht="152.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="47"/>
+    <row r="16" spans="1:10" ht="152.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="30"/>
       <c r="B16" s="18">
         <f t="shared" ref="B16" ca="1" si="2">IF(A16&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B16)-1,COLUMN(B16),4))+1)</f>
         <v>3</v>
@@ -6372,9 +6262,9 @@
       <c r="I16" s="14"/>
       <c r="J16" s="21"/>
     </row>
-    <row r="17" spans="1:9" ht="81" x14ac:dyDescent="0.15">
-      <c r="A17" s="47" t="s">
-        <v>252</v>
+    <row r="17" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="30" t="s">
+        <v>251</v>
       </c>
       <c r="B17" s="18">
         <f t="shared" ref="B17:B18" ca="1" si="3">IF(A17&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B17)-1,COLUMN(B17),4))+1)</f>
@@ -6400,8 +6290,8 @@
       </c>
       <c r="I17" s="14"/>
     </row>
-    <row r="18" spans="1:9" ht="81" x14ac:dyDescent="0.15">
-      <c r="A18" s="48"/>
+    <row r="18" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="31"/>
       <c r="B18" s="18">
         <f t="shared" ca="1" si="3"/>
         <v>2</v>
@@ -6435,12 +6325,7 @@
     <mergeCell ref="A6:H6"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="B9:B18">
-    <cfRule type="expression" dxfId="6" priority="2">
-      <formula>B9&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:A18">
+  <conditionalFormatting sqref="A9:B18">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>A9&lt;&gt;""</formula>
     </cfRule>
@@ -6470,25 +6355,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="25.125" customWidth="1"/>
-    <col min="5" max="5" width="42.75" customWidth="1"/>
-    <col min="6" max="6" width="41.75" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" customWidth="1"/>
+    <col min="2" max="2" width="8.59765625" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" customWidth="1"/>
+    <col min="4" max="4" width="25.1328125" customWidth="1"/>
+    <col min="5" max="5" width="42.73046875" customWidth="1"/>
+    <col min="6" max="6" width="41.73046875" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="43.5" customWidth="1"/>
-    <col min="9" max="9" width="19.25" customWidth="1"/>
+    <col min="8" max="8" width="43.46484375" customWidth="1"/>
+    <col min="9" max="9" width="19.265625" customWidth="1"/>
     <col min="10" max="10" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -6508,12 +6393,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="36">
+      <c r="B2" s="35"/>
+      <c r="C2" s="38">
         <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
         <v>1</v>
       </c>
@@ -6529,10 +6414,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="37"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="39"/>
       <c r="D3" s="17" t="str">
         <f>大中項目!B2</f>
         <v>JMS</v>
@@ -6545,7 +6430,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -6555,31 +6440,31 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A5" s="38" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="40"/>
-    </row>
-    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+    </row>
+    <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="43"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="45"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -6589,7 +6474,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -6618,7 +6503,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="str">
         <f>大中項目!C17</f>
         <v>JMSS0501</v>
@@ -6686,25 +6571,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="25.125" customWidth="1"/>
-    <col min="5" max="5" width="42.75" customWidth="1"/>
-    <col min="6" max="6" width="41.75" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" customWidth="1"/>
+    <col min="2" max="2" width="8.59765625" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" customWidth="1"/>
+    <col min="4" max="4" width="25.1328125" customWidth="1"/>
+    <col min="5" max="5" width="42.73046875" customWidth="1"/>
+    <col min="6" max="6" width="41.73046875" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="44.375" customWidth="1"/>
-    <col min="9" max="9" width="19.125" customWidth="1"/>
-    <col min="10" max="10" width="34.125" customWidth="1"/>
+    <col min="8" max="8" width="44.3984375" customWidth="1"/>
+    <col min="9" max="9" width="19.1328125" customWidth="1"/>
+    <col min="10" max="10" width="34.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -6724,12 +6609,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="36">
+      <c r="B2" s="35"/>
+      <c r="C2" s="38">
         <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
         <v>10</v>
       </c>
@@ -6745,10 +6630,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="37"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="39"/>
       <c r="D3" s="17" t="str">
         <f>大中項目!B2</f>
         <v>JMS</v>
@@ -6761,7 +6646,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -6771,31 +6656,31 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A5" s="38" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="40"/>
-    </row>
-    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+    </row>
+    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="43"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="45"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -6805,7 +6690,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -6834,9 +6719,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="104.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B9" s="18">
         <f t="shared" ref="B9:B16" ca="1" si="0">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
@@ -6863,7 +6748,7 @@
       <c r="I9" s="14"/>
       <c r="J9" s="21"/>
     </row>
-    <row r="10" spans="1:10" ht="132" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10" ht="132" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="B10" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -6890,9 +6775,9 @@
       <c r="I10" s="14"/>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10" ht="90.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B11" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -6902,7 +6787,7 @@
         <v>128</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E11" s="28" t="s">
         <v>131</v>
@@ -6919,7 +6804,7 @@
       <c r="I11" s="14"/>
       <c r="J11" s="21"/>
     </row>
-    <row r="12" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -6929,7 +6814,7 @@
         <v>126</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E12" s="28" t="s">
         <v>120</v>
@@ -6946,9 +6831,9 @@
       <c r="I12" s="14"/>
       <c r="J12" s="21"/>
     </row>
-    <row r="13" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B13" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -6958,16 +6843,16 @@
         <v>22</v>
       </c>
       <c r="D13" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="E13" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="F13" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="G13" s="28" t="s">
         <v>219</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>220</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>130</v>
@@ -6975,7 +6860,7 @@
       <c r="I13" s="14"/>
       <c r="J13" s="21"/>
     </row>
-    <row r="14" spans="1:10" ht="157.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10" ht="157.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
       <c r="B14" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -6985,26 +6870,26 @@
         <v>126</v>
       </c>
       <c r="D14" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="E14" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="F14" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="G14" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="H14" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="G14" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>224</v>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="21"/>
     </row>
-    <row r="15" spans="1:10" ht="126" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10" ht="126" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B15" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -7031,7 +6916,7 @@
       <c r="I15" s="14"/>
       <c r="J15" s="21"/>
     </row>
-    <row r="16" spans="1:10" ht="126" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10" ht="126" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="22"/>
       <c r="B16" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -7058,7 +6943,7 @@
       <c r="I16" s="14"/>
       <c r="J16" s="21"/>
     </row>
-    <row r="17" spans="1:10" ht="237.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10" ht="237.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22"/>
       <c r="B17" s="18">
         <v>5</v>
@@ -7070,10 +6955,10 @@
         <v>194</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>86</v>
@@ -7084,7 +6969,7 @@
       <c r="I17" s="14"/>
       <c r="J17" s="21"/>
     </row>
-    <row r="18" spans="1:10" ht="262.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10" ht="262.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="22"/>
       <c r="B18" s="18">
         <v>6</v>
@@ -7096,16 +6981,16 @@
         <v>194</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>86</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="21"/>
@@ -7149,25 +7034,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="25.125" customWidth="1"/>
-    <col min="5" max="5" width="42.75" customWidth="1"/>
-    <col min="6" max="6" width="41.75" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" customWidth="1"/>
+    <col min="2" max="2" width="8.59765625" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" customWidth="1"/>
+    <col min="4" max="4" width="25.1328125" customWidth="1"/>
+    <col min="5" max="5" width="42.73046875" customWidth="1"/>
+    <col min="6" max="6" width="41.73046875" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="43.5" customWidth="1"/>
-    <col min="9" max="9" width="19.25" customWidth="1"/>
+    <col min="8" max="8" width="43.46484375" customWidth="1"/>
+    <col min="9" max="9" width="19.265625" customWidth="1"/>
     <col min="10" max="10" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -7187,12 +7072,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="36">
+      <c r="B2" s="35"/>
+      <c r="C2" s="38">
         <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
         <v>8</v>
       </c>
@@ -7208,10 +7093,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="37"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="39"/>
       <c r="D3" s="17" t="str">
         <f>大中項目!B2</f>
         <v>JMS</v>
@@ -7224,7 +7109,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -7234,31 +7119,31 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A5" s="38" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="40"/>
-    </row>
-    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+    </row>
+    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="43"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="45"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -7268,7 +7153,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -7297,7 +7182,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="str">
         <f>大中項目!C22</f>
         <v>JMSS0701</v>
@@ -7326,7 +7211,7 @@
       </c>
       <c r="I9" s="14"/>
     </row>
-    <row r="10" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22"/>
       <c r="B10" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -7355,7 +7240,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="108" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10" ht="102" x14ac:dyDescent="0.25">
       <c r="A11" s="22"/>
       <c r="B11" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -7381,7 +7266,7 @@
       </c>
       <c r="I11" s="14"/>
     </row>
-    <row r="12" spans="1:10" ht="108" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10" ht="102" x14ac:dyDescent="0.25">
       <c r="A12" s="22"/>
       <c r="B12" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -7407,7 +7292,7 @@
       </c>
       <c r="I12" s="14"/>
     </row>
-    <row r="13" spans="1:10" ht="108" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10" ht="102" x14ac:dyDescent="0.25">
       <c r="A13" s="22"/>
       <c r="B13" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -7433,7 +7318,7 @@
       </c>
       <c r="I13" s="14"/>
     </row>
-    <row r="14" spans="1:10" ht="162" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10" ht="153" x14ac:dyDescent="0.25">
       <c r="A14" s="22"/>
       <c r="B14" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -7459,7 +7344,7 @@
       </c>
       <c r="I14" s="14"/>
     </row>
-    <row r="15" spans="1:10" ht="256.5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10" ht="242.25" x14ac:dyDescent="0.25">
       <c r="A15" s="22"/>
       <c r="B15" s="18">
         <f t="shared" ca="1" si="0"/>
@@ -7485,7 +7370,7 @@
       </c>
       <c r="I15" s="14"/>
     </row>
-    <row r="16" spans="1:10" ht="256.5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10" ht="242.25" x14ac:dyDescent="0.25">
       <c r="A16" s="22"/>
       <c r="B16" s="18">
         <f t="shared" ref="B16" ca="1" si="1">IF(A16&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B16)-1,COLUMN(B16),4))+1)</f>
@@ -7550,25 +7435,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="25.125" customWidth="1"/>
-    <col min="5" max="5" width="42.75" customWidth="1"/>
-    <col min="6" max="6" width="41.75" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" customWidth="1"/>
+    <col min="2" max="2" width="8.59765625" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" customWidth="1"/>
+    <col min="4" max="4" width="25.1328125" customWidth="1"/>
+    <col min="5" max="5" width="42.73046875" customWidth="1"/>
+    <col min="6" max="6" width="41.73046875" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="44.375" customWidth="1"/>
-    <col min="9" max="9" width="19.125" customWidth="1"/>
-    <col min="10" max="10" width="34.125" customWidth="1"/>
+    <col min="8" max="8" width="44.3984375" customWidth="1"/>
+    <col min="9" max="9" width="19.1328125" customWidth="1"/>
+    <col min="10" max="10" width="34.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
@@ -7588,12 +7473,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="36">
+      <c r="B2" s="35"/>
+      <c r="C2" s="38">
         <f ca="1">COUNTIFS($B$9:$B$65495,"&lt;&gt;",$J$9:$J$65495,"&lt;&gt;論理削除")</f>
         <v>4</v>
       </c>
@@ -7609,10 +7494,10 @@
       <c r="G2" s="9"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="37"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="39"/>
       <c r="D3" s="17" t="str">
         <f>大中項目!B2</f>
         <v>JMS</v>
@@ -7625,7 +7510,7 @@
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -7635,31 +7520,31 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A5" s="38" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="40"/>
-    </row>
-    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="41" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+    </row>
+    <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="43"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="45"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -7669,7 +7554,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
@@ -7698,38 +7583,38 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="50" t="s">
-        <v>229</v>
+    <row r="9" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>228</v>
       </c>
       <c r="B9" s="18">
         <f ca="1">IF(A9&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B9)-1,COLUMN(B9),4))+1)</f>
         <v>1</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="49" t="s">
+      <c r="D9" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="E9" s="45" t="s">
+      <c r="E9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="F9" s="45" t="s">
+      <c r="F9" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="H9" s="45" t="s">
-        <v>255</v>
-      </c>
-      <c r="I9" s="46"/>
+      <c r="H9" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="21"/>
     </row>
-    <row r="10" spans="1:10" ht="117" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10" ht="117" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B10" s="18">
         <f ca="1">IF(A10&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B10)-1,COLUMN(B10),4))+1)</f>
@@ -7756,9 +7641,9 @@
       <c r="I10" s="14"/>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10" ht="117" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10" ht="117" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B11" s="18">
         <f ca="1">IF(A11&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B11)-1,COLUMN(B11),4))+1)</f>
@@ -7780,12 +7665,12 @@
         <v>115</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="21"/>
     </row>
-    <row r="12" spans="1:10" ht="121.5" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A12" s="22"/>
       <c r="B12" s="18">
         <f ca="1">IF(A12&lt;&gt;"",1,INDIRECT(ADDRESS(ROW(B12)-1,COLUMN(B12),4))+1)</f>
